--- a/out/LSTM-Mamba1_repeat_5_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.703898596494605</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002391666291012662</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1029782065480331</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2062312347027925</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3978592722554057</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8992349143047647</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1223837424301584</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7456394706446274</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02483236514418547</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6727294146302889</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02150593183686688</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6908817635477288</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01051376199041308</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6903755990411835</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005015641485859501</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6898809185793132</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002086560232823799</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6890326334269331</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001444199058269057</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6898333499426518</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005999855152208458</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6895874190003919</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000309040657220384</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6896042393346734</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001183430603158046</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.68953151526076</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.199809157629899e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6895376040957872</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.83156321991085e-05</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6895315882241431</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.045194285233741e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.689524671152165</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.917577799040367e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6895175016822784</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.689511776624142</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6895060074812744</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.689500463813172</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6894955825149228</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6894955745438284</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6894957339657175</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6894959890407403</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.689495741936812</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6894957020813397</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.689495741936812</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6894958375899456</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6894957738211898</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6894957339657175</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6894954629485061</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6894953832375612</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6894954310641279</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.689495550630545</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6894955346883561</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.689495550630545</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6894955346883561</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.689495741936812</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6894959571563625</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6894958694743235</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6894958216477567</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6894958694743235</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6894956861391508</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6894956941102452</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6894957020813397</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6894957499079064</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6894958136766622</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6894959252719847</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6894959730985514</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6894959332430791</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6894958615032291</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6894959810696458</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6894958216477567</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6894955745438284</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6894955586016395</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6894954390352224</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6894953991797501</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6894956781680563</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6894956622258673</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6894955984571117</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6894954948328839</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6894953752664668</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6894954948328839</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.689495638312584</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6894955187461672</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6894955267172617</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.703898596494605</v>
+        <v>0.6525037326661627</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683207</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>0.6525037326661627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.703898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002391666291012662</v>
+        <v>-0.0002089631805759855</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1029782065480331</v>
+        <v>0.08997347853734741</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2062312347027925</v>
+        <v>0.1801870725006987</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3978592722554057</v>
+        <v>0.347614302979999</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.703898596494605</v>
+        <v>0.6525037326661628</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8992349143047647</v>
+        <v>0.7856739415146112</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1223837424301584</v>
+        <v>0.1069281082222289</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683207</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7456394706446274</v>
+        <v>0.6514751669176111</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02483236514418547</v>
+        <v>0.02169671512348328</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6727294146302889</v>
+        <v>0.5877721905053254</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02150593183686688</v>
+        <v>0.0187903195615987</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6908817635477288</v>
+        <v>0.6036321284946182</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01051376199041308</v>
+        <v>0.009185532746942296</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6903755990411835</v>
+        <v>0.6031896153749979</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005015641485859501</v>
+        <v>0.004381546626918769</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6898809185793132</v>
+        <v>0.6027567803693844</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002086560232823799</v>
+        <v>0.001822122886379481</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6890326334269331</v>
+        <v>0.6020150007223952</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001444199058269057</v>
+        <v>0.001261312915132866</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6898333499426518</v>
+        <v>0.6027140645186299</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005999855152208458</v>
+        <v>0.0005239596464284499</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6895874190003919</v>
+        <v>0.6024985218186313</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000309040657220384</v>
+        <v>0.000268950360553952</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6896042393346734</v>
+        <v>0.6025125804916073</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001183430603158046</v>
+        <v>0.0001025971377222977</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.68953151526076</v>
+        <v>0.6024483585644504</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.199809157629899e-05</v>
+        <v>5.398122591759655e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6895376040957872</v>
+        <v>0.6024530784265995</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.83156321991085e-05</v>
+        <v>2.379825834160227e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6895315882241431</v>
+        <v>0.6024471923291683</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.045194285233741e-05</v>
+        <v>8.853466005543883e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.689524671152165</v>
+        <v>0.602440502160975</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.917577799040367e-06</v>
+        <v>9.952340925016508e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6895175016822784</v>
+        <v>0.6024336219537401</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.689511776624142</v>
+        <v>0.6024279936429705</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6895060074812744</v>
+        <v>0.6024223211326862</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.689500463813172</v>
+        <v>0.6024167774645838</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.6024118563108624</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6894955825149228</v>
+        <v>0.6024118961663346</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6894955745438284</v>
+        <v>0.6024118881952402</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6894957339657175</v>
+        <v>0.6024120476171293</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6894959890407403</v>
+        <v>0.6024123026921521</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.689495741936812</v>
+        <v>0.6024120555882237</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6894957020813397</v>
+        <v>0.6024120157327515</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.6024120237038459</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.689495741936812</v>
+        <v>0.6024120555882237</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6894958375899456</v>
+        <v>0.6024121512413574</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6894957738211898</v>
+        <v>0.6024120874726016</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6894957339657175</v>
+        <v>0.6024120476171293</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.6024120237038459</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6894954629485061</v>
+        <v>0.6024117765999178</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6894953832375612</v>
+        <v>0.602411696888973</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6894954310641279</v>
+        <v>0.6024117447155397</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.689495550630545</v>
+        <v>0.6024118642819568</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6894955346883561</v>
+        <v>0.6024118483397679</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.689495550630545</v>
+        <v>0.6024118642819568</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6894955346883561</v>
+        <v>0.6024118483397679</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.6024119041374291</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.6024119041374291</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.6024119041374291</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.689495741936812</v>
+        <v>0.6024120555882237</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6894959571563625</v>
+        <v>0.6024122708077743</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6894958694743235</v>
+        <v>0.6024121831257353</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6894958216477567</v>
+        <v>0.6024121352991685</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6894958694743235</v>
+        <v>0.6024121831257353</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6894956861391508</v>
+        <v>0.6024119997905626</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6894956941102452</v>
+        <v>0.602412007761657</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6894957020813397</v>
+        <v>0.6024120157327515</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.6024120237038459</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6894957100524342</v>
+        <v>0.6024120237038459</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6894957499079064</v>
+        <v>0.6024120635593182</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6894958136766622</v>
+        <v>0.602412127328074</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6894959252719847</v>
+        <v>0.6024122389233965</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6894959730985514</v>
+        <v>0.6024122867499632</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6894959332430791</v>
+        <v>0.6024122468944909</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6894958615032291</v>
+        <v>0.6024121751546408</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6894959810696458</v>
+        <v>0.6024122947210576</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6894958216477567</v>
+        <v>0.6024121352991685</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6894955904860173</v>
+        <v>0.6024119041374291</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.6024118563108624</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6894955745438284</v>
+        <v>0.6024118881952402</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6894955586016395</v>
+        <v>0.6024118722530513</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6894954390352224</v>
+        <v>0.6024117526866342</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6894953991797501</v>
+        <v>0.6024117128311619</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.6024118563108624</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6894956781680563</v>
+        <v>0.6024119918194681</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6894956622258673</v>
+        <v>0.6024119758772792</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6894955984571117</v>
+        <v>0.6024119121085235</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6894954948328839</v>
+        <v>0.6024118084842957</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6894953752664668</v>
+        <v>0.6024116889178786</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6894954948328839</v>
+        <v>0.6024118084842957</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6894955426594506</v>
+        <v>0.6024118563108624</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.689495638312584</v>
+        <v>0.6024119519639958</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6894955187461672</v>
+        <v>0.602411832397579</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6894955267172617</v>
+        <v>0.6024118403686735</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01709672436118126</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009551443159580231</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005270447582006454</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.002875087782740593</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001664863899350166</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001191088929772377</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0008118245750665665</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0006539598107337952</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0007205698639154434</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0006688609719276428</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.000700976699590683</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.334101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0007043331861495972</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.334101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0008565858006477356</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.334101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001061590388417244</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.334101894739158</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001175766810774803</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001091314479708672</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0007315073162317276</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0004581790417432785</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0002773106098175049</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>4.957243800163269e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6525037326661627</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0001075249165296555</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0001308172941207886</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-6.272643804550171e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.02909442940683207</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>8.837133646011353e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6525037326661627</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>9.491853415966034e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0001026373356580734</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0001395326107740402</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0001740474253892899</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0003192853182554245</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0005758833140134811</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.00054146908223629</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0005605723708868027</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0005725119262933731</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.534101894739158</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0006316155195236206</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.334101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0007303562015295029</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.334101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0008979793637990952</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.334101894739158</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0010543093085289</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001168606802821159</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001414889469742775</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001480055972933769</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001722401008009911</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001587582752108574</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.334101894739158</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002089631805759855</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.08997347853734741</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.00160210020840168</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1801870725006987</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.347614302979999</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0008243396878242493</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6525037326661628</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7856739415146112</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1069281082222289</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001114821061491966</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.02909442940683207</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6514751669176111</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02169671512348328</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002469131723046303</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5877721905053254</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0187903195615987</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003797652199864388</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6036321284946182</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009185532746942296</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004246344789862633</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6031896153749979</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004381546626918769</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.004460321739315987</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6027567803693844</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001822122886379481</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.004396690055727959</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6020150007223952</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001261312915132866</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.004371901974081993</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6027140645186299</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005239596464284499</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003985477611422539</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6024985218186313</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000268950360553952</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003778213635087013</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6025125804916073</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001025971377222977</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003954818472266197</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6024483585644504</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.398122591759655e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.004014516249299049</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6024530784265995</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.379825834160227e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.004088165238499641</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6024471923291683</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.853466005543883e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003925910219550133</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.602440502160975</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.952340925016508e-07</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003677705302834511</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6024336219537401</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.519583929697793e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0034224484115839</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6024279936429705</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003173759207129478</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6024223211326862</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002966692671179771</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6024167774645838</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002711215987801552</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6024118563108624</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002670029178261757</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6024118961663346</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002467578276991844</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6024118881952402</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0025180634111166</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6024120476171293</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002284014597535133</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002501847222447395</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6024123026921521</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002855902537703514</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6024120555882237</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002984246239066124</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6024120157327515</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003120219334959984</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003143114969134331</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6024120237038459</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003075091168284416</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002238156273961067</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6024120555882237</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002375563606619835</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6024121512413574</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.002973029389977455</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6024120874726016</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003399791195988655</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6024120476171293</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003398185595870018</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6024120237038459</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003314672037959099</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6024117765999178</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003127897158265114</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.602411696888973</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002834869548678398</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6024117447155397</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002654442563652992</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6024118642819568</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002432627603411674</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6024118483397679</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002317143604159355</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6024118642819568</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002207914367318153</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6024118483397679</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002214232459664345</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6024119041374291</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00231478177011013</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6024119041374291</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.002083024010062218</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6024119041374291</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.002232125028967857</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6024120555882237</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00216272659599781</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6024122708077743</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002560747787356377</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6024121831257353</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002797113731503487</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6024121352991685</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002937695011496544</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6024121831257353</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003034962341189384</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6024119997905626</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003019804134964943</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.602412007761657</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.002848146483302116</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6024120157327515</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.002805484458804131</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6024120237038459</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002728095278143883</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6024120237038459</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002450002357363701</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6024120635593182</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002424096688628197</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.602412127328074</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002518506720662117</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6024122389233965</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002810338512063026</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6024122867499632</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002955587580800056</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6024122468944909</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002974828705191612</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6024121751546408</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003069540485739708</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6024122947210576</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003093427047133446</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6024121352991685</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003187766298651695</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6024119041374291</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003131868317723274</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6024118563108624</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003042010590434074</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6024118881952402</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002847516909241676</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002779668197035789</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002684799954295158</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6024118722530513</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002540720626711845</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6024117526866342</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002338549122214317</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6024117128311619</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002157343551516533</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6024118563108624</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002140047028660774</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6024119918194681</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002260392531752586</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6024119758772792</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00230816937983036</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002328870818018913</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6024119121085235</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002271460369229317</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6024118084842957</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002077000215649605</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6024116889178786</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002154534682631493</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6024118084842957</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002160647884011269</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6024118563108624</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002304738387465477</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6024119519639958</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002343172207474709</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.602411832397579</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002240663394331932</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6024118403686735</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01709672436118126</v>
+        <v>0.0170967411249876</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.009551443159580231</v>
+        <v>0.009551448747515678</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.005270447582006454</v>
+        <v>0.005270432680845261</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.002875087782740593</v>
+        <v>0.002875074744224548</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.001664863899350166</v>
+        <v>0.001664834097027779</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.001191088929772377</v>
+        <v>0.001191075891256332</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0008118245750665665</v>
+        <v>0.0008118432015180588</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.0006539598107337952</v>
+        <v>0.0006540082395076752</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0007205698639154434</v>
+        <v>0.0007205884903669357</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0006688609719276428</v>
+        <v>0.0006688591092824936</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.000700976699590683</v>
+        <v>0.0007009897381067276</v>
       </c>
       <c r="JB12" t="n">
         <v>0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0007043331861495972</v>
+        <v>0.0007043350487947464</v>
       </c>
       <c r="JB13" t="n">
         <v>0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0008565858006477356</v>
+        <v>0.0008565597236156464</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.001061590388417244</v>
+        <v>0.001061549410223961</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001175766810774803</v>
+        <v>0.001175753772258759</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.001091314479708672</v>
+        <v>0.001091277226805687</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0007315073162317276</v>
+        <v>0.0007314868271350861</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0004581790417432785</v>
+        <v>0.0004581697285175323</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0002773106098175049</v>
+        <v>0.0002772826701402664</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>4.957243800163269e-05</v>
+        <v>4.956498742103577e-05</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0001075249165296555</v>
+        <v>-0.0001075342297554016</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.0001308172941207886</v>
+        <v>-0.000130828469991684</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-6.272643804550171e-05</v>
+        <v>-6.273761391639709e-05</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>8.837133646011353e-05</v>
+        <v>8.834525942802429e-05</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>9.491853415966034e-05</v>
+        <v>9.492412209510803e-05</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0001026373356580734</v>
+        <v>0.000102633610367775</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0001395326107740402</v>
+        <v>0.000139530748128891</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0001740474253892899</v>
+        <v>0.0001740176230669022</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0003192853182554245</v>
+        <v>0.000319281592965126</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0005758833140134811</v>
+        <v>0.0005758907645940781</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.00054146908223629</v>
+        <v>0.0005414709448814392</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.2599999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0005605723708868027</v>
+        <v>0.0005605500191450119</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0005725119262933731</v>
+        <v>0.0005724877119064331</v>
       </c>
       <c r="JB34" t="n">
         <v>0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.0006316155195236206</v>
+        <v>0.000631578266620636</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0007303562015295029</v>
+        <v>0.0007303152233362198</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0008979793637990952</v>
+        <v>0.0008980110287666321</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0010543093085289</v>
+        <v>0.001054232940077782</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001168606802821159</v>
+        <v>0.001168558374047279</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001414889469742775</v>
+        <v>0.001414874568581581</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001480055972933769</v>
+        <v>0.001480011269450188</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.001722401008009911</v>
+        <v>0.001722332090139389</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.001587582752108574</v>
+        <v>0.001587489619851112</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.00160210020840168</v>
+        <v>0.001601945608854294</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.02000000000000007</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0008243396878242493</v>
+        <v>0.0008242987096309662</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001114821061491966</v>
+        <v>-0.001114875078201294</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.002469131723046303</v>
+        <v>-0.002469297498464584</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003797652199864388</v>
+        <v>-0.003797799348831177</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.004246344789862633</v>
+        <v>-0.004246529191732407</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.004460321739315987</v>
+        <v>-0.004460409283638</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.004396690055727959</v>
+        <v>-0.004396714270114899</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.004371901974081993</v>
+        <v>-0.004372008144855499</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.003985477611422539</v>
+        <v>-0.003985617309808731</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.003778213635087013</v>
+        <v>-0.003778312355279922</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.003954818472266197</v>
+        <v>-0.003954946994781494</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.004014516249299049</v>
+        <v>-0.004014622420072556</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.004088165238499641</v>
+        <v>-0.004088211804628372</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.003925910219550133</v>
+        <v>-0.003925982862710953</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.003677705302834511</v>
+        <v>-0.003677736967802048</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0034224484115839</v>
+        <v>-0.003422487527132034</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003173759207129478</v>
+        <v>-0.003173794597387314</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.002966692671179771</v>
+        <v>-0.002966731786727905</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002711215987801552</v>
+        <v>-0.00271124392747879</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002670029178261757</v>
+        <v>-0.002670064568519592</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002467578276991844</v>
+        <v>-0.002467624843120575</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0025180634111166</v>
+        <v>-0.002518098801374435</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002284014597535133</v>
+        <v>-0.002284064888954163</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002501847222447395</v>
+        <v>-0.002501912415027618</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.002855902537703514</v>
+        <v>-0.002855986356735229</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002984246239066124</v>
+        <v>-0.002984333783388138</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003120219334959984</v>
+        <v>-0.003120273351669312</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003143114969134331</v>
+        <v>-0.003143157809972763</v>
       </c>
       <c r="JB72" t="n">
         <v>0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003075091168284416</v>
+        <v>-0.003075107932090759</v>
       </c>
       <c r="JB73" t="n">
         <v>0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002238156273961067</v>
+        <v>-0.002238240092992783</v>
       </c>
       <c r="JB74" t="n">
         <v>0.5799999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002375563606619835</v>
+        <v>-0.00237559899687767</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.002973029389977455</v>
+        <v>-0.002973075956106186</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003399791195988655</v>
+        <v>-0.003399848937988281</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003398185595870018</v>
+        <v>-0.003398291766643524</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003314672037959099</v>
+        <v>-0.00331474095582962</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003127897158265114</v>
+        <v>-0.003127913922071457</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002834869548678398</v>
+        <v>-0.002834871411323547</v>
       </c>
       <c r="JB81" t="n">
         <v>0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002654442563652992</v>
+        <v>-0.002654414623975754</v>
       </c>
       <c r="JB82" t="n">
         <v>0.8599999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002432627603411674</v>
+        <v>-0.002432581037282944</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002317143604159355</v>
+        <v>-0.002317138016223907</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.002207914367318153</v>
+        <v>-0.002207912504673004</v>
       </c>
       <c r="JB85" t="n">
         <v>0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002214232459664345</v>
+        <v>-0.002214245498180389</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.00231478177011013</v>
+        <v>-0.002314794808626175</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.002083024010062218</v>
+        <v>-0.002083029597997665</v>
       </c>
       <c r="JB88" t="n">
         <v>0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.002232125028967857</v>
+        <v>-0.002232179045677185</v>
       </c>
       <c r="JB89" t="n">
         <v>0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.00216272659599781</v>
+        <v>-0.002162817865610123</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002560747787356377</v>
+        <v>-0.002560842782258987</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.002797113731503487</v>
+        <v>-0.002797100692987442</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.002937695011496544</v>
+        <v>-0.002937626093626022</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003034962341189384</v>
+        <v>-0.003034912049770355</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003019804134964943</v>
+        <v>-0.003019720315933228</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.002848146483302116</v>
+        <v>-0.002848107367753983</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.5799999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.002805484458804131</v>
+        <v>-0.002805452793836594</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.002728095278143883</v>
+        <v>-0.002728085964918137</v>
       </c>
       <c r="JB98" t="n">
         <v>0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002450002357363701</v>
+        <v>-0.002450000494718552</v>
       </c>
       <c r="JB99" t="n">
         <v>0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.002424096688628197</v>
+        <v>-0.002424135804176331</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002518506720662117</v>
+        <v>-0.002518586814403534</v>
       </c>
       <c r="JB101" t="n">
         <v>0.5799999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.002810338512063026</v>
+        <v>-0.002810407429933548</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002955587580800056</v>
+        <v>-0.002955727279186249</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002974828705191612</v>
+        <v>-0.00297488272190094</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003069540485739708</v>
+        <v>-0.003069587051868439</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003093427047133446</v>
+        <v>-0.003093469887971878</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003187766298651695</v>
+        <v>-0.003187783062458038</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003131868317723274</v>
+        <v>-0.003131948411464691</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003042010590434074</v>
+        <v>-0.003042075783014297</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002847516909241676</v>
+        <v>-0.002847567200660706</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002779668197035789</v>
+        <v>-0.002779699862003326</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002684799954295158</v>
+        <v>-0.002684816718101501</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002540720626711845</v>
+        <v>-0.002540722489356995</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002338549122214317</v>
+        <v>-0.002338547259569168</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002157343551516533</v>
+        <v>-0.002157352864742279</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002140047028660774</v>
+        <v>-0.002140048891305923</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002260392531752586</v>
+        <v>-0.002260394394397736</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.00230816937983036</v>
+        <v>-0.002308160066604614</v>
       </c>
       <c r="JB118" t="n">
         <v>0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002328870818018913</v>
+        <v>-0.002328865230083466</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002271460369229317</v>
+        <v>-0.002271436154842377</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002077000215649605</v>
+        <v>-0.002076972275972366</v>
       </c>
       <c r="JB121" t="n">
         <v>0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002154534682631493</v>
+        <v>-0.002154521644115448</v>
       </c>
       <c r="JB122" t="n">
         <v>0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002160647884011269</v>
+        <v>-0.002160649746656418</v>
       </c>
       <c r="JB123" t="n">
         <v>0.2599999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002304738387465477</v>
+        <v>-0.002304740250110626</v>
       </c>
       <c r="JB124" t="n">
         <v>0.1199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002343172207474709</v>
+        <v>-0.002343162894248962</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.09000000000000052</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002240663394331932</v>
+        <v>-0.002240661531686783</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3000000000000006</v>
